--- a/IOC_IP.xlsx
+++ b/IOC_IP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BeamStablizer\Documents\GitHub\DAQ_CA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\DAQ_CA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461E31DB-76CD-417E-9CD7-8B05B1F2BB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7809429E-AF01-4C45-9720-066B80465B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>PC Label</t>
   </si>
@@ -45,19 +45,75 @@
     <t>192.168.1.30</t>
   </si>
   <si>
+    <t>192.168.1.123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Python</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Focal Spot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CDS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy Tunner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Andor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DG645</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Faulhaber Stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>192.168.1.21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oriel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stages</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CA Server</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -85,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -363,37 +419,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>